--- a/Projektplanung.xlsx
+++ b/Projektplanung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\BK175055\ibrahim.k30\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Iaf43_Rechteck_Koc_Erdem-main\Iaf43_Rechteck_Koc_Erdem-main\Iaf43_Rechteck_Koc_Erdem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ACA8F5-D3B7-4EAC-8F55-8E09D91A6212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36B1BFE-1719-4DB1-8C94-7CD7357C156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -758,16 +758,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="88.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="88.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -776,12 +776,12 @@
       <c r="D1" s="14"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
@@ -790,12 +790,12 @@
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -812,7 +812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -827,7 +827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -842,7 +842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -857,7 +857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -872,7 +872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>5</v>
       </c>
@@ -887,7 +887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>6</v>
       </c>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>7</v>
       </c>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>8</v>
       </c>
@@ -932,7 +932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>9</v>
       </c>
@@ -947,7 +947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>10</v>
       </c>
@@ -962,7 +962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>11</v>
       </c>
@@ -977,7 +977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>12</v>
       </c>
@@ -992,21 +992,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1">
@@ -1016,84 +1016,84 @@
       <c r="D20" s="1"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1123,6 +1123,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008222CA67FD4B26498AE0BE8319BFCFED" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="74ea656ccc2034922b529965b6d92eae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18eb8cbc-be3b-4f77-b004-84c0dd024886" xmlns:ns3="75bbbc0f-8b65-433e-aee5-01fa35b453e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ca08b3b1bb2f18618cd59a32fa2530e" ns2:_="" ns3:_="">
     <xsd:import namespace="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
@@ -1351,17 +1362,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
   <ds:schemaRefs>
@@ -1371,6 +1371,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
+    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F11659F-E0B7-4449-8FB2-B7EF68A56D7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1387,15 +1398,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
-    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Projektplanung.xlsx
+++ b/Projektplanung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Iaf43_Rechteck_Koc_Erdem-main\Iaf43_Rechteck_Koc_Erdem-main\Iaf43_Rechteck_Koc_Erdem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\git neueste github\Iaf43_Rechteck_Koc_Erdem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36B1BFE-1719-4DB1-8C94-7CD7357C156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F1807-182F-4F83-9238-79A6EFEADAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Arbeitspaket</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>offen</t>
+  </si>
+  <si>
+    <t>Fertig</t>
   </si>
 </sst>
 </file>
@@ -824,7 +827,7 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1123,17 +1126,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008222CA67FD4B26498AE0BE8319BFCFED" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="74ea656ccc2034922b529965b6d92eae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18eb8cbc-be3b-4f77-b004-84c0dd024886" xmlns:ns3="75bbbc0f-8b65-433e-aee5-01fa35b453e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ca08b3b1bb2f18618cd59a32fa2530e" ns2:_="" ns3:_="">
     <xsd:import namespace="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
@@ -1362,6 +1354,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
   <ds:schemaRefs>
@@ -1371,17 +1374,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
-    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F11659F-E0B7-4449-8FB2-B7EF68A56D7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1398,4 +1390,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
+    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Projektplanung.xlsx
+++ b/Projektplanung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\git neueste github\Iaf43_Rechteck_Koc_Erdem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\BK175055\ibrahim.k30\Desktop\SWE POREJT wichtig!!! gg\Iaf43_Rechteck_Koc_Erdem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F1807-182F-4F83-9238-79A6EFEADAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11E522A-89E3-4E4C-80D4-597F7A092CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6855" yWindow="1770" windowWidth="21600" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Arbeitspaket</t>
   </si>
@@ -137,10 +137,16 @@
     <t>Sicherstellen, dass Breite und Höhe stets positive/gültige Werte enthalten</t>
   </si>
   <si>
-    <t>offen</t>
-  </si>
-  <si>
     <t>Fertig</t>
+  </si>
+  <si>
+    <t>Harun/Ibrahim</t>
+  </si>
+  <si>
+    <t>Harun</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
   </si>
 </sst>
 </file>
@@ -761,16 +767,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="88.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="88.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -779,12 +785,12 @@
       <c r="D1" s="14"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
@@ -793,12 +799,12 @@
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -815,7 +821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -825,12 +831,14 @@
       <c r="C6" s="6">
         <v>35</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E6" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -840,12 +848,14 @@
       <c r="C7" s="1">
         <v>40</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -855,12 +865,14 @@
       <c r="C8" s="1">
         <v>35</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -870,12 +882,14 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>5</v>
       </c>
@@ -885,12 +899,14 @@
       <c r="C10" s="1">
         <v>60</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E10" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>6</v>
       </c>
@@ -900,12 +916,14 @@
       <c r="C11" s="1">
         <v>50</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>7</v>
       </c>
@@ -915,12 +933,14 @@
       <c r="C12" s="1">
         <v>50</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>8</v>
       </c>
@@ -930,12 +950,14 @@
       <c r="C13" s="1">
         <v>80</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>9</v>
       </c>
@@ -945,12 +967,14 @@
       <c r="C14" s="1">
         <v>80</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>10</v>
       </c>
@@ -960,12 +984,14 @@
       <c r="C15" s="1">
         <v>40</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>11</v>
       </c>
@@ -975,12 +1001,14 @@
       <c r="C16" s="1">
         <v>30</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>12</v>
       </c>
@@ -990,26 +1018,28 @@
       <c r="C17" s="1">
         <v>20</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E17" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1">
@@ -1019,84 +1049,84 @@
       <c r="D20" s="1"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1117,12 +1147,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1355,20 +1387,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
+    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1393,12 +1426,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
-    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Projektplanung.xlsx
+++ b/Projektplanung.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\git neueste github\Iaf43_Rechteck_Koc_Erdem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - Georg-Simon-Ohm Berufskolleg\Desktop\Swe NEueste wichtigste beste PRojekt\Iaf43_Rechteck_Koc_Erdem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666F1807-182F-4F83-9238-79A6EFEADAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B57566E1-BD1D-4844-820F-27F683938120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Arbeitspaket</t>
   </si>
@@ -137,10 +137,19 @@
     <t>Sicherstellen, dass Breite und Höhe stets positive/gültige Werte enthalten</t>
   </si>
   <si>
-    <t>offen</t>
-  </si>
-  <si>
     <t>Fertig</t>
+  </si>
+  <si>
+    <t>Ibrahim/Harun</t>
+  </si>
+  <si>
+    <t>Harun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibrahim </t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
   </si>
 </sst>
 </file>
@@ -825,9 +834,11 @@
       <c r="C6" s="6">
         <v>35</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E6" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -840,7 +851,9 @@
       <c r="C7" s="1">
         <v>40</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>21</v>
       </c>
@@ -855,7 +868,9 @@
       <c r="C8" s="1">
         <v>35</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
@@ -870,7 +885,9 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
@@ -885,7 +902,9 @@
       <c r="C10" s="1">
         <v>60</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E10" s="7" t="s">
         <v>21</v>
       </c>
@@ -900,7 +919,9 @@
       <c r="C11" s="1">
         <v>50</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="E11" s="7" t="s">
         <v>21</v>
       </c>
@@ -915,7 +936,9 @@
       <c r="C12" s="1">
         <v>50</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="E12" s="7" t="s">
         <v>21</v>
       </c>
@@ -930,7 +953,9 @@
       <c r="C13" s="1">
         <v>80</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>21</v>
       </c>
@@ -945,7 +970,9 @@
       <c r="C14" s="1">
         <v>80</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E14" s="7" t="s">
         <v>21</v>
       </c>
@@ -960,7 +987,9 @@
       <c r="C15" s="1">
         <v>40</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E15" s="7" t="s">
         <v>21</v>
       </c>
@@ -975,7 +1004,9 @@
       <c r="C16" s="1">
         <v>30</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E16" s="7" t="s">
         <v>21</v>
       </c>
@@ -990,7 +1021,9 @@
       <c r="C17" s="1">
         <v>20</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E17" s="7" t="s">
         <v>21</v>
       </c>
@@ -1126,6 +1159,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008222CA67FD4B26498AE0BE8319BFCFED" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="74ea656ccc2034922b529965b6d92eae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18eb8cbc-be3b-4f77-b004-84c0dd024886" xmlns:ns3="75bbbc0f-8b65-433e-aee5-01fa35b453e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ca08b3b1bb2f18618cd59a32fa2530e" ns2:_="" ns3:_="">
     <xsd:import namespace="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
@@ -1354,17 +1398,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="18eb8cbc-be3b-4f77-b004-84c0dd024886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
   <ds:schemaRefs>
@@ -1374,6 +1407,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
+    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F11659F-E0B7-4449-8FB2-B7EF68A56D7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1390,15 +1434,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="75bbbc0f-8b65-433e-aee5-01fa35b453e8"/>
-    <ds:schemaRef ds:uri="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Projektplanung.xlsx
+++ b/Projektplanung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\BK175055\ibrahim.k30\Desktop\SWE POREJT wichtig!!! gg\Iaf43_Rechteck_Koc_Erdem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - Georg-Simon-Ohm Berufskolleg\Desktop\Swe NEueste wichtigste beste PRojekt\Iaf43_Rechteck_Koc_Erdem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11E522A-89E3-4E4C-80D4-597F7A092CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B57566E1-BD1D-4844-820F-27F683938120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6855" yWindow="1770" windowWidth="21600" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Arbeitspaket</t>
   </si>
@@ -140,10 +140,13 @@
     <t>Fertig</t>
   </si>
   <si>
-    <t>Harun/Ibrahim</t>
+    <t>Ibrahim/Harun</t>
   </si>
   <si>
     <t>Harun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibrahim </t>
   </si>
   <si>
     <t>Ibrahim</t>
@@ -767,16 +770,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="88.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="88.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -785,12 +788,12 @@
       <c r="D1" s="14"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
@@ -799,12 +802,12 @@
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -821,7 +824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -838,7 +841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -855,7 +858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -866,13 +869,13 @@
         <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -883,13 +886,13 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>5</v>
       </c>
@@ -906,7 +909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>6</v>
       </c>
@@ -917,13 +920,13 @@
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>7</v>
       </c>
@@ -934,13 +937,13 @@
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>8</v>
       </c>
@@ -957,7 +960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>9</v>
       </c>
@@ -968,13 +971,13 @@
         <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>10</v>
       </c>
@@ -985,13 +988,13 @@
         <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>11</v>
       </c>
@@ -1001,14 +1004,14 @@
       <c r="C16" s="1">
         <v>30</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>12</v>
       </c>
@@ -1018,28 +1021,28 @@
       <c r="C17" s="1">
         <v>20</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1">
@@ -1049,84 +1052,84 @@
       <c r="D20" s="1"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1147,6 +1150,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="75bbbc0f-8b65-433e-aee5-01fa35b453e8" xsi:nil="true"/>
@@ -1157,7 +1169,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008222CA67FD4B26498AE0BE8319BFCFED" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="74ea656ccc2034922b529965b6d92eae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18eb8cbc-be3b-4f77-b004-84c0dd024886" xmlns:ns3="75bbbc0f-8b65-433e-aee5-01fa35b453e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ca08b3b1bb2f18618cd59a32fa2530e" ns2:_="" ns3:_="">
     <xsd:import namespace="18eb8cbc-be3b-4f77-b004-84c0dd024886"/>
@@ -1386,16 +1398,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F848B79-804C-4409-80ED-AEEE314226E6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1406,7 +1417,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F11659F-E0B7-4449-8FB2-B7EF68A56D7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1423,12 +1434,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A012DDB2-1482-4C33-9164-B5CDE65A18C3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>